--- a/光伏配储项目/电价数据/2026/花都站.xlsx
+++ b/光伏配储项目/电价数据/2026/花都站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50845</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74236</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5715800000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5800299999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49441</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41371</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11583</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09420999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10249</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08637</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11245</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03554</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.0785</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09447</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06389</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08982999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.03172</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.03143</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14194</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21255</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2197</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21873</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21099</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.04899</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01209</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.22157</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11864</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.24276</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.24013</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17802</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.25786</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.52334</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.48476</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.71804</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.60164</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42714</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4353399999999999</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5709500000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6041299999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79028</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64164</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6049099999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73387</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.86883</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66135</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5862000000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.66311</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.48762</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.4357799999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62315</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.59999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48049</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6883899999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.16166</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.67092</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.73958</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.70865</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50302</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5176499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50473</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50441</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.4953</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5709099999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.55523</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42915</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.15285</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06216</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47565</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74282</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9537899999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.67088</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.4680299999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.39104</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.15143</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.47868</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22514</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.23512</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49386</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.59785</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.51022</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.66779</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6572899999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.71357</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.45135</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.43146</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.75459</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.44499</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.56972</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.48341</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43389</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42738</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33472</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50796</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47394</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.20218</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.22299</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.20388</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19215</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.16903</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26712</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48009</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.55352</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49156</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16838</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.45605</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.48547</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.51471</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.59845</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.54286</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.60499</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45209</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4174</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45221</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43883</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34202</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40877</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44742</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.1482</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23942</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.16884</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.16642</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5667000000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.06839000000000001</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.06788</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.20638</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6516900000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07149</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.17322</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45801</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42603</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.17153</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48662</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.48326</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5235599999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.43081</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29923</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28164</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.06128</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04493</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.06369</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.06189</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02671</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.02551</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.02828</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.01879</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.02339</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.02646</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.02699</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.01598</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03666</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04191</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.02005</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.03622</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03918</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.03842</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04515</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.02081</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.02655</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21933</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.06431999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.07315000000000001</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05933</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00397</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.02871</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09171</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40074</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46794</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65547</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44863</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42571</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.03554</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.11933</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00598</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.01426</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.01274</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.03868</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03611</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.02647</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.02856</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04742</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04795</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19968</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33562</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31712</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15941</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21397</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27055</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15656</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92037</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9138999999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8620599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29571</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88663</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6314299999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18622</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86833</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5443600000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.32997</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0323</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.52991</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79025</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53206</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77223</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77696</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8766799999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87348</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49246</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39899</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44915</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2061</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87878</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6209600000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5380900000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49743</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58778</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42903</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60345</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69536</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46785</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58229</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45211</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88493</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63554</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.84394</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.82356</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8617400000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44215</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26302</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35382</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91914</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46653</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46749</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41107</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50237</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26203</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19895</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19345</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27824</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.41412</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45095</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42158</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40295</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.60051</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89135</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35829</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16634</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70121</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7922400000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6690700000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58584</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45153</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43932</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41608</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5037900000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43532</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45311</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40466</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49583</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5419400000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.11526</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27228</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26959</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46461</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8706499999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4670299999999999</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32465</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27545</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22036</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13685</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14208</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27955</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15046</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14173</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13482</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14072</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13347</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2417</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13367</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25081</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25335</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13223</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.09104000000000001</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10499</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10521</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11577</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13226</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13656</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40074</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4561</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44121</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44541</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44435</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34938</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5414600000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47057</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41697</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26732</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19447</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24774</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24233</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24252</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41509</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36088</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39678</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43891</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.04372</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25114</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.08695</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22524</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27587</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43423</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.68902</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.21909</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29118</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.42102</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.42814</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.48279</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.41791</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35004</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4592</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6565800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7779299999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45359</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45989</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14832</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19798</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21433</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25279</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27609</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.15976</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.45922</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.68425</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63974</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.65224</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.53688</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.88054</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49499</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.86725</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5096499999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.51474</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.49895</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43206</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36071</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49132</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5295800000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48688</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41161</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42096</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45407</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45217</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56669</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50534</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45407</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.49021</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45123</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43947</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5224299999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43649</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41014</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6258899999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.18546</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.4949</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.54618</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.58849</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.7379</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.75993</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.04048</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.09155</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8138200000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58639</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52698</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83847</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7688700000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6233099999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67167</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44063</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4727</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48421</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47894</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47133</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4184</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55445</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44329</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45731</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44706</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45718</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18695</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46259</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47188</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10747</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18285</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41909</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43353</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36803</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44734</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27048</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22934</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22837</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24793</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24406</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14357</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24724</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04386</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27717</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16683</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23307</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25891</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26272</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23668</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35142</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22721</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27268</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01826</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15773</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.03178</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03965</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01492</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04384</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04197</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0488</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02423</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03013</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.01558</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02853</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01314</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03411</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21541</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.48692</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.40718</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.99524</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.9754299999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.47963</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.60064</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.47524</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.48938</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5678799999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.43199</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.43845</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46873</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.43131</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.47239</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.00525</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.07759</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.9451000000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.98922</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.43149</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.21041</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.18912</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.19308</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01527</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00742</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.08533</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25393</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32398</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.25155</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49523</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5212100000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.48221</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14047</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27428</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.45877</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46937</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4919</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2549</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47206</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44565</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46958</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.57392</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41531</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45902</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23818</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36879</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43082</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49435</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57177</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5620299999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.4372200000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5668</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.62573</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49539</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5221399999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5606</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.61253</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.73619</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7008099999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.6095900000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.53323</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.53352</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37296</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14234</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.25365</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05827</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13335</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02441</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20284</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15487</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00774</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25813</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14671</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05741</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04242</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06647</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.18197</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07162</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.22019</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15909</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.19183</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48566</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42232</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42951</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38794</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06979</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.57662</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46639</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41822</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.14672</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01781</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.02499</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03622</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.008150000000000001</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04043</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.009210000000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.0007700000000000001</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15399</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03795</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.18669</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37028</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48783</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.18609</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.15546</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.21292</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.12259</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.22875</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04703</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04901</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04501</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04115</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.10261</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02818</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.07947</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.13206</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.24376</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16497</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05133</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.21403</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15396</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.26452</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40787</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47996</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39811</v>
       </c>
     </row>
   </sheetData>
